--- a/reports/ASX_Strong_Buy_Screener_2026-07-28.xlsx
+++ b/reports/ASX_Strong_Buy_Screener_2026-07-28.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report generated: 2026-07-28 00:48 </t>
+          <t xml:space="preserve">Report generated: 2026-07-28 23:45 </t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>7.18</v>
+        <v>7.19</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>9.970000000000001</v>
@@ -926,13 +926,13 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.03</v>
+        <v>0.0305</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.0599</v>
+        <v>0.0611</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1199</v>
+        <v>0.1221</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>28.72</v>
+        <v>28.76</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>1.38</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>8.365</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>10.63</v>
@@ -1143,13 +1143,13 @@
         <v>7.94</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.0618</v>
+        <v>0.0579</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.1236</v>
+        <v>0.1158</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.2471</v>
+        <v>0.2317</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="J5" s="5" t="n">
-        <v>10.09</v>
+        <v>10.21</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.95</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7.215</v>
+        <v>7.33</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7.75</v>
@@ -1210,13 +1210,13 @@
         <v>6.54</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.0071</v>
+        <v>0.0039</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.0142</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.0285</v>
+        <v>0.0158</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>36.08</v>
+        <v>36.65</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>12.45</v>
+        <v>12.65</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.25</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>38.54</v>
+        <v>38.9</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>39.43</v>
@@ -1277,13 +1277,13 @@
         <v>26.44</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-0.0031</v>
+        <v>-0.0054</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.0062</v>
+        <v>-0.0108</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-0.0124</v>
+        <v>-0.0216</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>110.11</v>
+        <v>111.14</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>1.22</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>63.615</v>
+        <v>63.79</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>73.29000000000001</v>
@@ -1344,13 +1344,13 @@
         <v>44.18</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0063</v>
+        <v>0.0056</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.0126</v>
+        <v>0.0112</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.0252</v>
+        <v>0.0224</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>26.84</v>
+        <v>26.92</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6.21</v>
+        <v>6.23</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>6.06</v>
+        <v>6.08</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.31</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>21.73</v>
+        <v>21.82</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>26.17</v>
@@ -1411,13 +1411,13 @@
         <v>17.67</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0282</v>
+        <v>0.0305</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.0565</v>
+        <v>0.0611</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.113</v>
+        <v>0.1221</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>34.49</v>
+        <v>34.63</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>6.49</v>
+        <v>6.52</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.92</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5.54</v>
@@ -1553,13 +1553,13 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.0095</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.019</v>
+        <v>-0.0171</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.038</v>
+        <v>-0.0342</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>28.28</v>
+        <v>28.17</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>1.27</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>46.16</v>
+        <v>46.06</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>0.3</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>64.48</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>76.40000000000001</v>
@@ -1620,13 +1620,13 @@
         <v>51.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0263</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.056</v>
+        <v>0.0527</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.112</v>
+        <v>0.1053</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1634,13 +1634,13 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>36.02</v>
+        <v>36.4</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>1.44</v>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1674,11 +1674,11 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>AMP FPO [AMP]</t>
+          <t>AMP Limited</t>
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2.125</v>
+        <v>2.14</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>2.2</v>
@@ -1687,13 +1687,13 @@
         <v>1.14</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-0.0142</v>
+        <v>-0.0117</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>-0.0285</v>
+        <v>-0.0234</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-0.0569</v>
+        <v>-0.0467</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>32.69</v>
+        <v>32.68</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>37.54</v>
@@ -1756,13 +1756,13 @@
         <v>25.05</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.0131</v>
+        <v>0.0112</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.0262</v>
+        <v>0.0224</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.0525</v>
+        <v>0.0448</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>24.58</v>
+        <v>24.57</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>1.65</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1810,11 +1810,11 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ANZ GROUP FPO [ANZ]</t>
+          <t>ANZ Group Holdings Limited</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>36.76</v>
+        <v>37.22</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>41</v>
@@ -1823,13 +1823,13 @@
         <v>29.85</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.0091</v>
+        <v>-0.0121</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.0242</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.0366</v>
+        <v>-0.0485</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>18.66</v>
+        <v>18.89</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>10.26</v>
+        <v>10.28</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>11.1</v>
@@ -1894,13 +1894,13 @@
         <v>8.220000000000001</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>-0.022</v>
+        <v>-0.0225</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>-0.044</v>
+        <v>-0.0449</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.0881</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>85.5</v>
+        <v>85.67</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>4.77</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>21.72</v>
+        <v>22.59</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>35.64</v>
@@ -1961,13 +1961,13 @@
         <v>18.59</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.0443</v>
+        <v>0.033</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.0886</v>
+        <v>0.066</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.1773</v>
+        <v>0.1319</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>24.97</v>
+        <v>25.97</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="M17" s="9" t="n">
         <v>1.54</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>18.68</v>
+        <v>18.94</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>41.34</v>
@@ -2103,13 +2103,13 @@
         <v>16.93</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.0594</v>
+        <v>0.0551</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.1188</v>
+        <v>0.1103</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.2375</v>
+        <v>0.2205</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>17.46</v>
+        <v>17.7</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>5.82</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>4.1</v>
@@ -2170,13 +2170,13 @@
         <v>3.05</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.0597</v>
+        <v>0.0587</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.1194</v>
+        <v>0.1175</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.2389</v>
+        <v>0.235</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0.98</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>11.16</v>
+        <v>11.2</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.32</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>54.81</v>
+        <v>55.26</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>71.29000000000001</v>
@@ -2237,13 +2237,13 @@
         <v>44.3</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0062</v>
+        <v>0.0041</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.0247</v>
+        <v>0.0163</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>20.38</v>
+        <v>20.54</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.12</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>28.08</v>
+        <v>28.32</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>40.28</v>
@@ -2304,13 +2304,13 @@
         <v>22.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0572</v>
+        <v>0.0546</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.1144</v>
+        <v>0.1092</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.2287</v>
+        <v>0.2183</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>17.44</v>
+        <v>17.59</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="M22" s="9" t="n">
         <v>0.65</v>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:45</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.407</v>
+        <v>0.43</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>4.14</v>
@@ -2513,13 +2513,13 @@
         <v>0.355</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.1113</v>
+        <v>0.0919</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.2225</v>
+        <v>0.1839</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.445</v>
+        <v>0.3677</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -2527,13 +2527,13 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>12.43</v>
+        <v>13.13</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>0.91</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11.02</v>
+        <v>11.15</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>13.73</v>
@@ -2580,13 +2580,13 @@
         <v>9.81</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0121</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>-0.0186</v>
+        <v>-0.0242</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>-0.0372</v>
+        <v>-0.0484</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>12.95</v>
+        <v>13.1</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>6.72</v>
@@ -2649,13 +2649,13 @@
         <v>4.93</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0136</v>
+        <v>0.0144</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0.0271</v>
+        <v>0.0288</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.0543</v>
+        <v>0.0577</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>206.67</v>
+        <v>206</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>0.52</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>59.35</v>
+        <v>59.37</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>65.98</v>
@@ -2716,13 +2716,13 @@
         <v>39.18</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.005</v>
+        <v>0.0052</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.0198</v>
+        <v>0.021</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>20.61</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>5.59</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>6.46</v>
+        <v>6.56</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>8.07</v>
@@ -3008,13 +3008,13 @@
         <v>5.91</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>-0.0074</v>
+        <v>-0.0111</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>-0.0147</v>
+        <v>-0.0221</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-0.0294</v>
+        <v>-0.0442</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -3022,13 +3022,13 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>43.07</v>
+        <v>43.73</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3064,26 +3064,26 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BEACH FPO [BPT]</t>
+          <t>Beach Energy Limited</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1.37</v>
+        <v>1.355</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0542</v>
+        <v>0.043</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.1084</v>
+        <v>0.0861</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.2167</v>
+        <v>0.1721</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J33" s="5" t="n">
-        <v>4.97</v>
+        <v>5.16</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>30.63</v>
+        <v>31.76</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>37.11</v>
@@ -3146,13 +3146,13 @@
         <v>25.41</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.035</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.091</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.1821</v>
+        <v>0.14</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>32.94</v>
+        <v>34.15</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>0.28</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3200,11 +3200,11 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>BLUESCOPE FPO [BSL]</t>
+          <t>BlueScope Steel Limited</t>
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>32.24</v>
+        <v>32</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>34.14</v>
@@ -3213,13 +3213,13 @@
         <v>20.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0166</v>
+        <v>0.0186</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.0332</v>
+        <v>0.0372</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.0664</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>56.56</v>
+        <v>56.14</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>19.195</v>
+        <v>19.25</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>26.93</v>
@@ -3349,13 +3349,13 @@
         <v>16.18</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0305</v>
+        <v>0.0302</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.061</v>
+        <v>0.0605</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.1219</v>
+        <v>0.121</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>19.99</v>
+        <v>20.05</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>5.34</v>
+        <v>5.36</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.85</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>42.06</v>
@@ -3416,13 +3416,13 @@
         <v>21.47</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.0814</v>
+        <v>0.062</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.1628</v>
+        <v>0.124</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.3256</v>
+        <v>0.2479</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>32.1</v>
+        <v>33.82</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>7.71</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>0.51</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>175.5</v>
+        <v>178.78</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>185.59</v>
@@ -3483,13 +3483,13 @@
         <v>146.98</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.075</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.15</v>
+        <v>-0.1564</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.2999</v>
+        <v>-0.3128</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>28.22</v>
+        <v>28.74</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>10.31</v>
+        <v>10.5</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>13.7</v>
+        <v>13.73</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>18.48</v>
@@ -3552,13 +3552,13 @@
         <v>9.5</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.0755</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.1511</v>
+        <v>0.1497</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0.3022</v>
+        <v>0.2993</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>2.04</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>10.5</v>
+        <v>10.54</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>10.85</v>
@@ -3694,13 +3694,13 @@
         <v>7.25</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>-0.0043</v>
+        <v>-0.0053</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0105</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>-0.0173</v>
+        <v>-0.021</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
@@ -3708,13 +3708,13 @@
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>16.94</v>
+        <v>17</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>1.96</v>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>23.12</v>
+        <v>23.28</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>25.95</v>
@@ -3761,13 +3761,13 @@
         <v>18.18</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0125</v>
+        <v>0.0129</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.0251</v>
+        <v>0.0259</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.0501</v>
+        <v>0.0517</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -3775,13 +3775,13 @@
         </is>
       </c>
       <c r="J43" s="5" t="n">
-        <v>20.64</v>
+        <v>20.79</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>12.7</v>
+        <v>12.79</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>0.18</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3828,13 +3828,13 @@
         <v>3.75</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.1068</v>
+        <v>0.1078</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.2136</v>
+        <v>0.2156</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.4273</v>
+        <v>0.4312</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>11.91</v>
+        <v>12.28</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="L44" s="9" t="n">
         <v>1.24</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3.59</v>
@@ -3895,13 +3895,13 @@
         <v>2.83</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0264</v>
+        <v>0.0255</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.051</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.102</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -3909,13 +3909,13 @@
         </is>
       </c>
       <c r="J45" s="5" t="n">
-        <v>13.82</v>
+        <v>13.86</v>
       </c>
       <c r="K45" s="5" t="n">
         <v>0.77</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.58</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>8.074999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>12.73</v>
@@ -3962,13 +3962,13 @@
         <v>7.64</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.0679</v>
+        <v>0.0693</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.1358</v>
+        <v>0.1386</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.2716</v>
+        <v>0.2772</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>20.71</v>
+        <v>20.62</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>0.6</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>3.745</v>
+        <v>3.81</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>4.66</v>
@@ -4029,13 +4029,13 @@
         <v>3.3</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0141</v>
+        <v>0.01</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.0281</v>
+        <v>0.0199</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0.0562</v>
+        <v>0.0398</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="J47" s="5" t="n">
-        <v>12.08</v>
+        <v>12.29</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>0.57</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>8.960000000000001</v>
@@ -4163,13 +4163,13 @@
         <v>7.44</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0137</v>
+        <v>0.0142</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.0273</v>
+        <v>0.0283</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.0547</v>
+        <v>0.0567</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="J49" s="5" t="n">
-        <v>158.4</v>
+        <v>158.6</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>11.11</v>
+        <v>11.12</v>
       </c>
       <c r="L49" s="5" t="n">
         <v>3.37</v>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>117.74</v>
+        <v>119.88</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>319.56</v>
@@ -4230,13 +4230,13 @@
         <v>88.73999999999999</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.0111</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>0.0316</v>
+        <v>0.0221</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>0.0633</v>
+        <v>0.0443</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>22.3</v>
+        <v>22.75</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="M50" s="5" t="n">
         <v>0.12</v>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>23.75</v>
+        <v>23.79</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>24.59</v>
@@ -4297,13 +4297,13 @@
         <v>20.1</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.0005</v>
+        <v>-0.0009</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.001</v>
+        <v>-0.0019</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.0021</v>
+        <v>-0.0037</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>31.25</v>
+        <v>31.3</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>0.71</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4351,11 +4351,11 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>CSHARE FPO [CPU]</t>
+          <t>Computershare Limited</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>40.35</v>
+        <v>40.55</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>42.275</v>
@@ -4364,13 +4364,13 @@
         <v>26.73</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>-0.0155</v>
+        <v>-0.0164</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>-0.0311</v>
+        <v>-0.0327</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>-0.0622</v>
+        <v>-0.0654</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>27.45</v>
+        <v>27.77</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="D53" s="10" t="n">
         <v>4.31</v>
@@ -4433,13 +4433,13 @@
         <v>3.56</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>0.0179</v>
+        <v>0.0166</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>0.0358</v>
+        <v>0.0332</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.0717</v>
+        <v>0.0663</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -4447,13 +4447,13 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>6.62</v>
+        <v>6.76</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="M53" s="9" t="n">
         <v>0.45</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Q53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4487,11 +4487,11 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>CSL FPO [CSL]</t>
+          <t>CSL Limited</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>116.95</v>
+        <v>119.52</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>275.79</v>
@@ -4500,13 +4500,13 @@
         <v>90</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0466</v>
+        <v>0.0406</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0813</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>0.1866</v>
+        <v>0.1626</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>13.21</v>
+        <v>13.55</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>14</v>
@@ -4636,13 +4636,13 @@
         <v>8.35</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0.3434</v>
+        <v>0.3372</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>0.6867</v>
+        <v>0.6744</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>1.3735</v>
+        <v>1.3488</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4650,13 +4650,13 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>15.23</v>
+        <v>15.33</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="M56" s="9" t="n">
         <v>0.13</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="C57" s="10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="D57" s="10" t="n">
         <v>2.96</v>
@@ -4703,13 +4703,13 @@
         <v>2.14</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0609</v>
+        <v>0.0596</v>
       </c>
       <c r="G57" s="11" t="n">
-        <v>0.1219</v>
+        <v>0.1193</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0.2438</v>
+        <v>0.2386</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M57" s="9" t="n">
         <v>0.8</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="Q57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>17.7</v>
+        <v>17.06</v>
       </c>
       <c r="D59" s="6" t="n">
         <v>24.58</v>
@@ -4845,13 +4845,13 @@
         <v>13.11</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0376</v>
+        <v>0.046</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.0752</v>
+        <v>0.0919</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.1505</v>
+        <v>0.1839</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="J59" s="5" t="n">
-        <v>27.66</v>
+        <v>27.08</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="M59" s="5" t="n">
         <v>1.81</v>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>7.86</v>
+        <v>7.89</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>8.654999999999999</v>
@@ -4912,13 +4912,13 @@
         <v>6.72</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0146</v>
+        <v>0.0136</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.0293</v>
+        <v>0.0272</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0.0585</v>
+        <v>0.0545</v>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>32.75</v>
+        <v>32.88</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>0.51</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>4.78</v>
@@ -4979,13 +4979,13 @@
         <v>3.67</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0267</v>
+        <v>0.023</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0535</v>
+        <v>0.046</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.107</v>
+        <v>0.092</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="J61" s="5" t="n">
-        <v>12.5</v>
+        <v>12.65</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>16.22</v>
+        <v>16.41</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>8.26</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>1.13</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>5.755</v>
+        <v>5.87</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>7.73</v>
@@ -5046,13 +5046,13 @@
         <v>5.3</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0463</v>
+        <v>0.0383</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0.0925</v>
+        <v>0.0766</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.1851</v>
+        <v>0.1532</v>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>12.51</v>
+        <v>12.76</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="M62" s="5" t="n">
         <v>0.47</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C63" s="10" t="n">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="D63" s="10" t="n">
         <v>7.91</v>
@@ -5113,13 +5113,13 @@
         <v>4.96</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.0463</v>
+        <v>0.0369</v>
       </c>
       <c r="G63" s="11" t="n">
-        <v>0.0925</v>
+        <v>0.0737</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>0.185</v>
+        <v>0.1474</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -5127,13 +5127,13 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>22</v>
+        <v>22.72</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="M63" s="9" t="n">
         <v>0.79</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Q63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5171,22 +5171,22 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1.16</v>
+        <v>1.145</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>0.285</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.5258</v>
+        <v>0.5383</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>1.0516</v>
+        <v>1.0766</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>2.1032</v>
+        <v>2.1532</v>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
@@ -5194,13 +5194,13 @@
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>7.24</v>
+        <v>7.12</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="M64" s="5" t="n">
         <v>0.57</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5234,11 +5234,11 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>EVOLUTION FPO [EVN]</t>
+          <t>Evolution Mining Limited</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>17.75</v>
@@ -5247,13 +5247,13 @@
         <v>6.96</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.031</v>
+        <v>0.0308</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.0621</v>
+        <v>0.0617</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.1241</v>
+        <v>0.1234</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="J65" s="5" t="n">
-        <v>17.11</v>
+        <v>17.12</v>
       </c>
       <c r="K65" s="5" t="n">
         <v>4.07</v>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>3.44</v>
@@ -5316,13 +5316,13 @@
         <v>2.22</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>-0.0211</v>
+        <v>-0.0218</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>-0.0422</v>
+        <v>-0.0437</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>-0.0844</v>
+        <v>-0.0873</v>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J66" s="5" t="n">
-        <v>20.95</v>
+        <v>20.97</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0.48</v>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>12.27</v>
+        <v>12.64</v>
       </c>
       <c r="D67" s="10" t="n">
         <v>16.56</v>
@@ -5383,13 +5383,13 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.0487</v>
+        <v>0.04</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>0.0975</v>
+        <v>0.08</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.1949</v>
+        <v>0.16</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>24.54</v>
+        <v>25.28</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="M67" s="9" t="n">
         <v>1.09</v>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="Q67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>18.58</v>
+        <v>18.7</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>23.38</v>
@@ -5450,13 +5450,13 @@
         <v>17.68</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.0022</v>
+        <v>0.0009</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.0044</v>
+        <v>0.0019</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0038</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>10.68</v>
+        <v>10.75</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="M68" s="5" t="n">
         <v>0.28</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>33.27</v>
+        <v>33.57</v>
       </c>
       <c r="D69" s="10" t="n">
         <v>35.31</v>
@@ -5517,13 +5517,13 @@
         <v>26.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.0225</v>
+        <v>0.0209</v>
       </c>
       <c r="G69" s="11" t="n">
-        <v>0.0449</v>
+        <v>0.0418</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>0.0898</v>
+        <v>0.0835</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -5531,13 +5531,13 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>50.41</v>
+        <v>50.86</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>11.14</v>
+        <v>11.24</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M69" s="9" t="n">
         <v>6.91</v>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="Q69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5571,11 +5571,11 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>GOOD GROUP STAPLED [GMG]</t>
+          <t>Goodman Group</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>29.42</v>
+        <v>29.58</v>
       </c>
       <c r="D70" s="10" t="n">
         <v>37.31</v>
@@ -5584,13 +5584,13 @@
         <v>24.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>0.0463</v>
+        <v>0.0438</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>0.0927</v>
+        <v>0.0876</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0.1854</v>
+        <v>0.1752</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>35.02</v>
+        <v>35.21</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>9.130000000000001</v>
@@ -5653,13 +5653,13 @@
         <v>4.69</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0294</v>
+        <v>0.0231</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0.0589</v>
+        <v>0.0462</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.1177</v>
+        <v>0.0924</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>25.35</v>
+        <v>25.94</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="L71" s="5" t="n">
         <v>0.18</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:48</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>2.185</v>
+        <v>2.21</v>
       </c>
       <c r="D73" s="10" t="n">
         <v>2.68</v>
@@ -5795,13 +5795,13 @@
         <v>2.07</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0.0578</v>
+        <v>0.0543</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>0.1156</v>
+        <v>0.1086</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>0.2311</v>
+        <v>0.2172</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -5809,13 +5809,13 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>43.7</v>
+        <v>44.2</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>0.85</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Q73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>5.75</v>
@@ -5862,13 +5862,13 @@
         <v>4.42</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>0.0208</v>
+        <v>0.0181</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>0.0415</v>
+        <v>0.0362</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>0.083</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>9.92</v>
+        <v>10.02</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>9.34</v>
+        <v>9.43</v>
       </c>
       <c r="M74" s="5" t="n">
         <v>0.53</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>83.09</v>
+        <v>83.97</v>
       </c>
       <c r="D77" s="10" t="n">
         <v>122.03</v>
@@ -6071,13 +6071,13 @@
         <v>68.7</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.0476</v>
+        <v>0.0444</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>0.0951</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>0.1902</v>
+        <v>0.1778</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>64.41</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>12.44</v>
+        <v>12.57</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>14.99</v>
+        <v>15.15</v>
       </c>
       <c r="M77" s="9" t="n">
         <v>0.11</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="Q77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>4.775</v>
+        <v>4.83</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>7.7</v>
@@ -6138,13 +6138,13 @@
         <v>4.28</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>0.0212</v>
+        <v>0.0181</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.0423</v>
+        <v>0.0362</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0.0847</v>
+        <v>0.0723</v>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
@@ -6152,13 +6152,13 @@
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>10.61</v>
+        <v>10.73</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M78" s="5" t="n">
         <v>0.5</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6192,11 +6192,11 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>INSUR.AUST FPO [IAG]</t>
+          <t>Insurance Australia Group Limited</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>8.654999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D79" s="6" t="n">
         <v>9.17</v>
@@ -6205,13 +6205,13 @@
         <v>6.39</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.0046</v>
+        <v>-0.0033</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.0092</v>
+        <v>-0.0067</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.0185</v>
+        <v>-0.0134</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>18.82</v>
+        <v>18.72</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2.115</v>
+        <v>2.22</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>6.735</v>
@@ -6274,13 +6274,13 @@
         <v>1.995</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0.2468</v>
+        <v>0.2233</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0.4937</v>
+        <v>0.4467</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0.9873</v>
+        <v>0.8933</v>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
@@ -6288,13 +6288,13 @@
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>70.5</v>
+        <v>74</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="M80" s="5" t="n">
         <v>0.9</v>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>6.87</v>
+        <v>6.99</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>10.05</v>
@@ -6416,13 +6416,13 @@
         <v>4.1</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0.0496</v>
+        <v>0.0324</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0.1983</v>
+        <v>0.1297</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="J82" s="5" t="n">
-        <v>8.74</v>
+        <v>10.64</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>11.88</v>
+        <v>12.09</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>1.02</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Q82" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6483,13 +6483,13 @@
         <v>4.9</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.0752</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G83" s="11" t="n">
-        <v>0.1505</v>
+        <v>0.1468</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0.301</v>
+        <v>0.2936</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>-17.25</v>
+        <v>-19.29</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>1.27</v>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="Q83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>6.24</v>
@@ -6550,13 +6550,13 @@
         <v>3.64</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>0.0435</v>
+        <v>0.0415</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0829</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.174</v>
+        <v>0.1659</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>12.68</v>
+        <v>12.76</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="M84" s="9" t="n">
         <v>0.58</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="Q84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>3.56</v>
@@ -6617,13 +6617,13 @@
         <v>1.69</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0135</v>
+        <v>0.0112</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.0269</v>
+        <v>0.0223</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.0538</v>
+        <v>0.0446</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>15.13</v>
+        <v>15.27</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="L85" s="5" t="n">
         <v>0.27</v>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>5.655</v>
@@ -6684,27 +6684,27 @@
         <v>3.155</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.0289</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.0512</v>
+        <v>0.0577</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>0.1024</v>
+        <v>0.1154</v>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>15.29</v>
+        <v>15.11</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M86" s="5" t="n">
         <v>0.65</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>6.67</v>
+        <v>6.76</v>
       </c>
       <c r="D88" s="10" t="n">
         <v>10.38</v>
@@ -6826,13 +6826,13 @@
         <v>5.64</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.1077</v>
+        <v>0.1029</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>0.2154</v>
+        <v>0.2059</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.4308</v>
+        <v>0.4118</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -6840,13 +6840,13 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>16.27</v>
+        <v>16.49</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="M88" s="9" t="n">
         <v>0.39</v>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="Q88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>77.08</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>121</v>
@@ -6968,13 +6968,13 @@
         <v>67.38</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>0.0078</v>
+        <v>0.004</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0.0155</v>
+        <v>0.0081</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0.0311</v>
+        <v>0.0161</v>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
@@ -6982,13 +6982,13 @@
         </is>
       </c>
       <c r="J90" s="5" t="n">
-        <v>17.52</v>
+        <v>17.76</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>5.02</v>
+        <v>5.09</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="M90" s="5" t="n">
         <v>0.43</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>38.02</v>
+        <v>38.06</v>
       </c>
       <c r="D92" s="10" t="n">
         <v>45.98</v>
@@ -7110,13 +7110,13 @@
         <v>24.41</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>-0.0017</v>
+        <v>0.0009</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>-0.0035</v>
+        <v>0.0018</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>-0.0069</v>
+        <v>0.0037</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>140.81</v>
+        <v>140.96</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>2.4</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="M92" s="9" t="n">
         <v>0.74</v>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="D93" s="6" t="n">
         <v>5.22</v>
@@ -7177,13 +7177,13 @@
         <v>3.63</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.0534</v>
+        <v>0.0457</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.1067</v>
+        <v>0.0914</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.2134</v>
+        <v>0.1828</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
@@ -7191,13 +7191,13 @@
         </is>
       </c>
       <c r="J93" s="5" t="n">
-        <v>17.71</v>
+        <v>18.17</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="M93" s="5" t="n">
         <v>1.13</v>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>2.895</v>
+        <v>2.89</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>5.95</v>
@@ -7244,13 +7244,13 @@
         <v>2.4</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0953</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0.1894</v>
+        <v>0.1906</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0.3787</v>
+        <v>0.3811</v>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>0.36</v>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>14.75</v>
+        <v>14.68</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>22.37</v>
@@ -7386,13 +7386,13 @@
         <v>10.365</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0.0599</v>
+        <v>0.0613</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0.1197</v>
+        <v>0.1227</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0.2395</v>
+        <v>0.2454</v>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
@@ -7400,13 +7400,13 @@
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>184.38</v>
+        <v>183.5</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>20.74</v>
+        <v>20.64</v>
       </c>
       <c r="M96" s="5" t="n">
         <v>6.32</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>9.795</v>
+        <v>9.76</v>
       </c>
       <c r="D97" s="6" t="n">
         <v>11.8</v>
@@ -7453,13 +7453,13 @@
         <v>7.96</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.0115</v>
+        <v>-0.0106</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.0212</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-0.0459</v>
+        <v>-0.0425</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>12.09</v>
+        <v>12.05</v>
       </c>
       <c r="K97" s="5" t="n">
         <v>1.72</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>10.91</v>
+        <v>10.87</v>
       </c>
       <c r="M97" s="5" t="n">
         <v>0.38</v>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>1.74</v>
+        <v>1.755</v>
       </c>
       <c r="D98" s="10" t="n">
         <v>2.46</v>
@@ -7520,13 +7520,13 @@
         <v>1.607</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.0445</v>
+        <v>0.0418</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0.0891</v>
+        <v>0.0835</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.1782</v>
+        <v>0.1671</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -7534,13 +7534,13 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>17.4</v>
+        <v>17.55</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0.75</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="M98" s="9" t="n">
         <v>0.44</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="Q98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>53.09</v>
+        <v>53.1</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>74.94</v>
@@ -7587,13 +7587,13 @@
         <v>27.65</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.0713</v>
+        <v>0.0706</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.1426</v>
+        <v>0.1411</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.2822</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="J99" s="5" t="n">
-        <v>26.28</v>
+        <v>26.29</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>2.8</v>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>5.125</v>
+        <v>5.18</v>
       </c>
       <c r="D100" s="6" t="n">
         <v>5.28</v>
@@ -7654,13 +7654,13 @@
         <v>4.06</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>-0.0022</v>
+        <v>-0.0048</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>-0.0044</v>
+        <v>-0.0097</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0193</v>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
@@ -7668,13 +7668,13 @@
         </is>
       </c>
       <c r="J100" s="5" t="n">
-        <v>30.15</v>
+        <v>30.47</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>6.02</v>
+        <v>6.08</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M100" s="5" t="n">
         <v>0.12</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7708,11 +7708,11 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>MACQ GROUP FPO [MQG]</t>
+          <t>Macquarie Group Limited</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>253.9</v>
+        <v>256.47</v>
       </c>
       <c r="D101" s="6" t="n">
         <v>260.57</v>
@@ -7734,15 +7734,11 @@
           <t>No data</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+      <c r="J101" s="5" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>2.71</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
@@ -7771,7 +7767,7 @@
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7783,11 +7779,11 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>METCASHLTD FPO [MTS]</t>
+          <t>Metcash Limited</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="D102" s="6" t="n">
         <v>4.26</v>
@@ -7796,13 +7792,13 @@
         <v>2.63</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.0339</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0.0698</v>
+        <v>0.0679</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>0.1395</v>
+        <v>0.1358</v>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
@@ -7810,10 +7806,10 @@
         </is>
       </c>
       <c r="J102" s="5" t="n">
-        <v>12.16</v>
+        <v>12.2</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
@@ -7840,7 +7836,7 @@
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7852,11 +7848,11 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>NAT. BANK FPO [NAB]</t>
+          <t>National Australia Bank Limited</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>40.84</v>
+        <v>41.21</v>
       </c>
       <c r="D103" s="6" t="n">
         <v>49.45</v>
@@ -7865,13 +7861,13 @@
         <v>35.48</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.0166</v>
+        <v>-0.0189</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.0332</v>
+        <v>-0.0379</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.0665</v>
+        <v>-0.0757</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -7879,12 +7875,10 @@
         </is>
       </c>
       <c r="J103" s="5" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>20.61</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>2.08</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
@@ -7913,7 +7907,7 @@
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7923,7 @@
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="D104" s="10" t="n">
         <v>4.77</v>
@@ -7938,13 +7932,13 @@
         <v>2.94</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>0.1007</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>0.2015</v>
+        <v>0.1992</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0.403</v>
+        <v>0.3984</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -7952,13 +7946,13 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>43.43</v>
+        <v>43.57</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="M104" s="9" t="n">
         <v>3.04</v>
@@ -7980,7 +7974,7 @@
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7990,7 @@
         </is>
       </c>
       <c r="C105" s="10" t="n">
-        <v>0.957</v>
+        <v>0.975</v>
       </c>
       <c r="D105" s="10" t="n">
         <v>1.9</v>
@@ -8005,13 +7999,13 @@
         <v>0.835</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.1757</v>
+        <v>0.1632</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0.3514</v>
+        <v>0.3265</v>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
@@ -8019,13 +8013,13 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>13.67</v>
+        <v>13.93</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>0.17</v>
@@ -8047,7 +8041,7 @@
       </c>
       <c r="Q105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8057,7 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>7.545</v>
+        <v>7.58</v>
       </c>
       <c r="D106" s="6" t="n">
         <v>8.26</v>
@@ -8072,13 +8066,13 @@
         <v>5.79</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>0.0091</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.0182</v>
+        <v>0.0158</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0317</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
@@ -8086,10 +8080,10 @@
         </is>
       </c>
       <c r="J106" s="5" t="n">
-        <v>18.86</v>
+        <v>18.95</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="L106" s="5" t="n">
         <v>0.99</v>
@@ -8114,7 +8108,7 @@
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8183,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8199,7 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>20.1</v>
+        <v>20.25</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>31.96</v>
@@ -8214,13 +8208,13 @@
         <v>15.3</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>0.0587</v>
+        <v>0.0564</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.1173</v>
+        <v>0.1127</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>0.2346</v>
+        <v>0.2255</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
@@ -8228,13 +8222,13 @@
         </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>17.18</v>
+        <v>17.31</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0.12</v>
@@ -8256,7 +8250,7 @@
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:46</t>
         </is>
       </c>
     </row>
@@ -8268,11 +8262,11 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>NUFARM FPO [NUF]</t>
+          <t>Nufarm Limited</t>
         </is>
       </c>
       <c r="C109" s="6" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="D109" s="6" t="n">
         <v>3.1</v>
@@ -8281,13 +8275,13 @@
         <v>1.79</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v/>
+        <v>0.0465</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v/>
+        <v>0.093</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v/>
+        <v>0.186</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -8295,10 +8289,10 @@
         </is>
       </c>
       <c r="J109" s="5" t="n">
-        <v>15.21</v>
+        <v>15.01</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
@@ -8325,7 +8319,7 @@
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8335,7 @@
         </is>
       </c>
       <c r="C110" s="6" t="n">
-        <v>21.29</v>
+        <v>21.72</v>
       </c>
       <c r="D110" s="6" t="n">
         <v>38.3</v>
@@ -8350,13 +8344,13 @@
         <v>19.805</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>0.0697</v>
+        <v>0.0633</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.1393</v>
+        <v>0.1267</v>
       </c>
       <c r="H110" s="7" t="n">
-        <v>0.2786</v>
+        <v>0.2533</v>
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
@@ -8364,13 +8358,13 @@
         </is>
       </c>
       <c r="J110" s="5" t="n">
-        <v>92.56999999999999</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>34.9</v>
+        <v>35.61</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>14.46</v>
+        <v>14.75</v>
       </c>
       <c r="M110" s="5" t="n">
         <v>8.369999999999999</v>
@@ -8392,7 +8386,7 @@
       </c>
       <c r="Q110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8402,7 @@
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>44.185</v>
+        <v>44.43</v>
       </c>
       <c r="D111" s="10" t="n">
         <v>57.16</v>
@@ -8417,13 +8411,13 @@
         <v>36.01</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.0549</v>
+        <v>0.0517</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>0.1098</v>
+        <v>0.1035</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>0.2196</v>
+        <v>0.2069</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -8431,13 +8425,13 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>39.1</v>
+        <v>39.32</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>0.32</v>
@@ -8459,7 +8453,7 @@
       </c>
       <c r="Q111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8469,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>13.48</v>
+        <v>13.23</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>18.22</v>
@@ -8484,13 +8478,13 @@
         <v>10.91</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>0.1232</v>
+        <v>0.1302</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>0.2463</v>
+        <v>0.2604</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.4926</v>
+        <v>0.5208</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
@@ -8498,13 +8492,13 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>-33.38</v>
+        <v>-32.76</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>22.6</v>
+        <v>22.19</v>
       </c>
       <c r="M112" s="9" t="n">
         <v>0.6</v>
@@ -8526,7 +8520,7 @@
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8536,7 @@
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="D113" s="6" t="n">
         <v>2.43</v>
@@ -8551,13 +8545,13 @@
         <v>1.212</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>0.0504</v>
+        <v>0.0418</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.2015</v>
+        <v>0.1672</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -8565,13 +8559,13 @@
         </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0.29</v>
@@ -8593,7 +8587,7 @@
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8603,7 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>10.5</v>
+        <v>10.64</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>13.13</v>
@@ -8618,13 +8612,13 @@
         <v>10.02</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>0.0307</v>
+        <v>0.027</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>0.0615</v>
+        <v>0.0541</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>0.1229</v>
+        <v>0.1082</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -8632,13 +8626,13 @@
         </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>17.8</v>
+        <v>18.03</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="M114" s="5" t="n">
         <v>0.48</v>
@@ -8660,7 +8654,7 @@
       </c>
       <c r="Q114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8672,11 +8666,11 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>ORICA FPO [ORI]</t>
+          <t>Orica Limited</t>
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>23.595</v>
+        <v>23.67</v>
       </c>
       <c r="D115" s="10" t="n">
         <v>26.47</v>
@@ -8685,13 +8679,13 @@
         <v>18.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.0239</v>
+        <v>0.023</v>
       </c>
       <c r="G115" s="11" t="n">
-        <v>0.0477</v>
+        <v>0.046</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0.0954</v>
+        <v>0.092</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -8699,10 +8693,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>46.26</v>
+        <v>46.41</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="L115" s="9" t="inlineStr">
         <is>
@@ -8729,7 +8723,7 @@
       </c>
       <c r="Q115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8798,7 @@
       </c>
       <c r="Q116" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8814,7 @@
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>4.175</v>
+        <v>4.04</v>
       </c>
       <c r="D117" s="6" t="n">
         <v>6.81</v>
@@ -8829,13 +8823,13 @@
         <v>1.58</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0873</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0.1527</v>
+        <v>0.1745</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>0.3054</v>
+        <v>0.349</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -8843,13 +8837,13 @@
         </is>
       </c>
       <c r="J117" s="5" t="n">
-        <v>11.51</v>
+        <v>11.14</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>13.91</v>
+        <v>13.46</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0.2</v>
@@ -8871,7 +8865,7 @@
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8887,22 +8881,22 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>159.59</v>
+        <v>163.14</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>324.5</v>
+        <v>324.49</v>
       </c>
       <c r="E118" s="10" t="n">
         <v>107.75</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0.0487</v>
+        <v>0.0417</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>0.0974</v>
+        <v>0.0834</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0.1948</v>
+        <v>0.1667</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -8910,13 +8904,13 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>71.25</v>
+        <v>72.83</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>42.88</v>
+        <v>43.83</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>69.3</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="M118" s="9" t="n">
         <v>0.66</v>
@@ -8938,7 +8932,7 @@
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8948,7 @@
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>13.935</v>
+        <v>13.56</v>
       </c>
       <c r="D119" s="10" t="n">
         <v>22.92</v>
@@ -8963,13 +8957,13 @@
         <v>10.97</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0.0442</v>
+        <v>0.0523</v>
       </c>
       <c r="G119" s="11" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1047</v>
       </c>
       <c r="H119" s="11" t="n">
-        <v>0.1768</v>
+        <v>0.2094</v>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
@@ -8977,13 +8971,13 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>15.48</v>
+        <v>15.07</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>0.24</v>
@@ -9005,7 +8999,7 @@
       </c>
       <c r="Q119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9015,7 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>19.7</v>
+        <v>20.18</v>
       </c>
       <c r="D120" s="10" t="n">
         <v>22.32</v>
@@ -9030,13 +9024,13 @@
         <v>15.1</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>0.0116</v>
+        <v>0.0054</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>0.0232</v>
+        <v>0.0108</v>
       </c>
       <c r="H120" s="11" t="n">
-        <v>0.0464</v>
+        <v>0.0215</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -9044,13 +9038,13 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>11.53</v>
+        <v>11.81</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="M120" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -9072,7 +9066,7 @@
       </c>
       <c r="Q120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9082,7 @@
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>10.38</v>
+        <v>10.39</v>
       </c>
       <c r="D121" s="10" t="n">
         <v>12.62</v>
@@ -9097,13 +9091,13 @@
         <v>8.035</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0.0294</v>
+        <v>0.0291</v>
       </c>
       <c r="G121" s="11" t="n">
-        <v>0.0588</v>
+        <v>0.0582</v>
       </c>
       <c r="H121" s="11" t="n">
-        <v>0.1176</v>
+        <v>0.1165</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
@@ -9111,10 +9105,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>11.69</v>
+        <v>11.7</v>
       </c>
       <c r="L121" s="9" t="n">
         <v>0.64</v>
@@ -9139,7 +9133,7 @@
       </c>
       <c r="Q121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9151,11 +9145,11 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>QBE INSUR. FPO [QBE]</t>
+          <t>QBE Insurance Group Limited</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>25.385</v>
+        <v>25.52</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>25.83</v>
@@ -9164,13 +9158,13 @@
         <v>18.57</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>-0.01</v>
+        <v>-0.0112</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>-0.0199</v>
+        <v>-0.0223</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>-0.0398</v>
+        <v>-0.0447</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -9178,10 +9172,10 @@
         </is>
       </c>
       <c r="J122" s="5" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
@@ -9208,7 +9202,7 @@
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9269,7 @@
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9285,7 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>158.51</v>
+        <v>162.99</v>
       </c>
       <c r="D124" s="6" t="n">
         <v>265.98</v>
@@ -9300,13 +9294,13 @@
         <v>131.07</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>0.0505</v>
+        <v>0.0415</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>0.101</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>0.202</v>
+        <v>0.1661</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -9314,13 +9308,13 @@
         </is>
       </c>
       <c r="J124" s="5" t="n">
-        <v>36.52</v>
+        <v>37.56</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>10.18</v>
+        <v>10.47</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="M124" s="5" t="n">
         <v>4.3</v>
@@ -9342,7 +9336,7 @@
       </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9352,7 @@
         </is>
       </c>
       <c r="C125" s="6" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="D125" s="6" t="n">
         <v>44.73</v>
@@ -9367,13 +9361,13 @@
         <v>30.39</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>0.0016</v>
+        <v>0.0003</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.0032</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.0064</v>
+        <v>0.0013</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -9381,13 +9375,13 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>34.13</v>
+        <v>34.44</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="M125" s="5" t="n">
         <v>2.07</v>
@@ -9409,7 +9403,7 @@
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9421,11 +9415,11 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>RIO TINTO FPO [RIO]</t>
+          <t>Rio Tinto Group</t>
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>159.91</v>
+        <v>159.53</v>
       </c>
       <c r="D126" s="6" t="n">
         <v>195.84</v>
@@ -9434,13 +9428,13 @@
         <v>110.31</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>0.0171</v>
+        <v>0.0179</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>0.0342</v>
+        <v>0.0358</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0716</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -9448,12 +9442,10 @@
         </is>
       </c>
       <c r="J126" s="5" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="K126" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>18.36</v>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>2.91</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
@@ -9480,7 +9472,7 @@
       </c>
       <c r="Q126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9488,7 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>28.59</v>
+        <v>28.95</v>
       </c>
       <c r="D127" s="10" t="n">
         <v>45.25</v>
@@ -9505,13 +9497,13 @@
         <v>25.5</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>0.1005</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G127" s="11" t="n">
-        <v>0.2009</v>
+        <v>0.1934</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>0.4019</v>
+        <v>0.3867</v>
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
@@ -9519,13 +9511,13 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>19.19</v>
+        <v>19.56</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>7.49</v>
+        <v>7.58</v>
       </c>
       <c r="M127" s="9" t="n">
         <v>0.13</v>
@@ -9547,7 +9539,7 @@
       </c>
       <c r="Q127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9555,7 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>6.09</v>
+        <v>6.14</v>
       </c>
       <c r="D128" s="6" t="n">
         <v>10</v>
@@ -9572,13 +9564,13 @@
         <v>3.95</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>0.0566</v>
+        <v>0.0541</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>0.1132</v>
+        <v>0.1082</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>0.2264</v>
+        <v>0.2165</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -9586,13 +9578,13 @@
         </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>9.52</v>
+        <v>9.59</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="M128" s="5" t="n">
         <v>5.8</v>
@@ -9614,7 +9606,7 @@
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9622,7 @@
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="D129" s="10" t="n">
         <v>4.62</v>
@@ -9639,13 +9631,13 @@
         <v>2.86</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.0529</v>
+        <v>0.0504</v>
       </c>
       <c r="G129" s="11" t="n">
-        <v>0.1058</v>
+        <v>0.1008</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>0.2116</v>
+        <v>0.2016</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -9653,13 +9645,13 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>18.84</v>
+        <v>19</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M129" s="9" t="n">
         <v>0.33</v>
@@ -9681,7 +9673,7 @@
       </c>
       <c r="Q129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9689,7 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>4.465</v>
+        <v>4.52</v>
       </c>
       <c r="D130" s="6" t="n">
         <v>4.95</v>
@@ -9706,13 +9698,13 @@
         <v>2.52</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>0.0151</v>
+        <v>0.0123</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.0303</v>
+        <v>0.0245</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>0.0605</v>
+        <v>0.0491</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -9720,13 +9712,13 @@
         </is>
       </c>
       <c r="J130" s="5" t="n">
-        <v>37.21</v>
+        <v>37.67</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="M130" s="5" t="n">
         <v>0.18</v>
@@ -9748,7 +9740,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9756,7 @@
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>3.905</v>
+        <v>3.95</v>
       </c>
       <c r="D131" s="6" t="n">
         <v>4.27</v>
@@ -9773,13 +9765,13 @@
         <v>3.275</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>0.0115</v>
+        <v>0.0095</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>0.0229</v>
+        <v>0.0191</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.0459</v>
+        <v>0.0382</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -9787,13 +9779,13 @@
         </is>
       </c>
       <c r="J131" s="5" t="n">
-        <v>11.49</v>
+        <v>11.62</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
       <c r="M131" s="5" t="n">
         <v>0.79</v>
@@ -9815,7 +9807,7 @@
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9876,7 @@
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9892,7 @@
         </is>
       </c>
       <c r="C133" s="6" t="n">
-        <v>5.285</v>
+        <v>5.24</v>
       </c>
       <c r="D133" s="6" t="n">
         <v>6.665</v>
@@ -9909,13 +9901,13 @@
         <v>3.87</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>0.0232</v>
+        <v>0.0255</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.0464</v>
+        <v>0.051</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.0927</v>
+        <v>0.1021</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -9923,13 +9915,13 @@
         </is>
       </c>
       <c r="J133" s="5" t="n">
-        <v>16.52</v>
+        <v>16.38</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="M133" s="5" t="n">
         <v>0.76</v>
@@ -9951,7 +9943,7 @@
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9959,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>13.29</v>
+        <v>14.06</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>29.84</v>
@@ -9976,13 +9968,13 @@
         <v>11.745</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>0.145</v>
+        <v>0.1209</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>0.2899</v>
+        <v>0.2418</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>0.5799</v>
+        <v>0.4837</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -9990,13 +9982,13 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>20.32</v>
+        <v>21.81</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>3.94</v>
+        <v>4.17</v>
       </c>
       <c r="M134" s="9" t="n">
         <v>0.54</v>
@@ -10018,7 +10010,7 @@
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10026,7 @@
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>26.27</v>
+        <v>25.83</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>31.81</v>
@@ -10043,13 +10035,13 @@
         <v>13.04</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>0.026</v>
+        <v>0.0307</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.0519</v>
+        <v>0.0613</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.1039</v>
+        <v>0.1227</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -10057,13 +10049,13 @@
         </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>14.03</v>
+        <v>13.79</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M135" s="5" t="n">
         <v>0.29</v>
@@ -10085,7 +10077,7 @@
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10093,7 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="D136" s="6" t="n">
         <v>6.75</v>
@@ -10110,13 +10102,13 @@
         <v>3.71</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>0.0476</v>
+        <v>0.042</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0839</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0.1904</v>
+        <v>0.1679</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -10124,13 +10116,13 @@
         </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>11.53</v>
+        <v>11.75</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="M136" s="5" t="n">
         <v>0.5600000000000001</v>
@@ -10152,7 +10144,7 @@
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10160,7 @@
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D137" s="6" t="n">
         <v>0.195</v>
@@ -10177,13 +10169,13 @@
         <v>0.08</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -10191,13 +10183,13 @@
         </is>
       </c>
       <c r="J137" s="5" t="n">
-        <v>-9.380000000000001</v>
+        <v>-10.16</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="M137" s="5" t="n">
         <v>0.65</v>
@@ -10219,7 +10211,7 @@
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10227,7 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>21.57</v>
+        <v>22.01</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>29.24</v>
@@ -10244,13 +10236,13 @@
         <v>18.26</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>0.0259</v>
+        <v>0.0203</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>0.0517</v>
+        <v>0.0407</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>0.1034</v>
+        <v>0.0814</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -10258,13 +10250,13 @@
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>19.43</v>
+        <v>20.01</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="M138" s="5" t="n">
         <v>0.68</v>
@@ -10286,7 +10278,7 @@
       </c>
       <c r="Q138" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10353,7 @@
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10369,7 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>45.42</v>
+        <v>45.38</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>46.79</v>
@@ -10386,13 +10378,13 @@
         <v>34.78</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>-0.0289</v>
+        <v>-0.0287</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>-0.0577</v>
+        <v>-0.0573</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>-0.1155</v>
+        <v>-0.1147</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -10428,7 +10420,7 @@
       </c>
       <c r="Q140" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10440,11 +10432,11 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>SANTOS FPO [STO]</t>
+          <t>Santos Limited</t>
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>7.615</v>
+        <v>7.77</v>
       </c>
       <c r="D141" s="10" t="n">
         <v>8.24</v>
@@ -10453,13 +10445,13 @@
         <v>5.9</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>0.0332</v>
+        <v>0.0268</v>
       </c>
       <c r="G141" s="11" t="n">
-        <v>0.0664</v>
+        <v>0.0537</v>
       </c>
       <c r="H141" s="11" t="n">
-        <v>0.1327</v>
+        <v>0.1074</v>
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
@@ -10467,10 +10459,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>21.15</v>
+        <v>21.58</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="L141" s="9" t="inlineStr">
         <is>
@@ -10497,7 +10489,7 @@
       </c>
       <c r="Q141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10505,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>13.085</v>
+        <v>13.24</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>20.2</v>
@@ -10522,13 +10514,13 @@
         <v>10.08</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>0.0142</v>
+        <v>0.0111</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>0.0284</v>
+        <v>0.0222</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>0.0568</v>
+        <v>0.0444</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -10536,13 +10528,13 @@
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>15.22</v>
+        <v>15.4</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="M142" s="5" t="n">
         <v>1</v>
@@ -10564,7 +10556,7 @@
       </c>
       <c r="Q142" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10572,7 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>19.42</v>
+        <v>19.54</v>
       </c>
       <c r="D143" s="6" t="n">
         <v>21.92</v>
@@ -10589,13 +10581,13 @@
         <v>13.8</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>-0.0018</v>
+        <v>-0.0034</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>-0.0037</v>
+        <v>-0.0067</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>-0.0073</v>
+        <v>-0.0134</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -10603,10 +10595,10 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>23.4</v>
+        <v>23.54</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="L143" s="5" t="n">
         <v>1.37</v>
@@ -10631,7 +10623,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10698,7 @@
       </c>
       <c r="Q144" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10714,7 @@
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>0.877</v>
+        <v>0.87</v>
       </c>
       <c r="D145" s="6" t="n">
         <v>1.19</v>
@@ -10731,13 +10723,13 @@
         <v>0.66</v>
       </c>
       <c r="F145" s="7" t="n">
-        <v>0.0335</v>
+        <v>0.035</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0701</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>0.1341</v>
+        <v>0.1401</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -10745,10 +10737,10 @@
         </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>87.7</v>
+        <v>87</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L145" s="5" t="n">
         <v>0.76</v>
@@ -10773,7 +10765,7 @@
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10785,11 +10777,11 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>TRANSURBAN STAPLED [TCL]</t>
+          <t>Transurban Group</t>
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>14.54</v>
+        <v>14.72</v>
       </c>
       <c r="D146" s="6" t="n">
         <v>15.62</v>
@@ -10798,13 +10790,13 @@
         <v>13.25</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>-0.0098</v>
+        <v>-0.0128</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>-0.0197</v>
+        <v>-0.0256</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>-0.0394</v>
+        <v>-0.0511</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -10812,10 +10804,10 @@
         </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>96.93000000000001</v>
+        <v>98.13</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
@@ -10842,7 +10834,7 @@
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10854,11 +10846,11 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>TELSTRA FPO [TLS]</t>
+          <t>Telstra Group Limited</t>
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>4.955</v>
+        <v>5.01</v>
       </c>
       <c r="D147" s="6" t="n">
         <v>5.58</v>
@@ -10867,13 +10859,13 @@
         <v>4.705</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>0.0135</v>
+        <v>0.0106</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>0.027</v>
+        <v>0.0212</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>0.0541</v>
+        <v>0.0425</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -10881,10 +10873,10 @@
         </is>
       </c>
       <c r="J147" s="5" t="n">
-        <v>24.77</v>
+        <v>25.05</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
@@ -10911,7 +10903,7 @@
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10919,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>29.39</v>
+        <v>29.63</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>41.44</v>
@@ -10936,13 +10928,13 @@
         <v>20.14</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>0.0151</v>
+        <v>0.0129</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>0.0301</v>
+        <v>0.0258</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>0.0602</v>
+        <v>0.0517</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -10950,13 +10942,13 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>68.34999999999999</v>
+        <v>68.91</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>22.44</v>
+        <v>22.62</v>
       </c>
       <c r="L148" s="9" t="n">
-        <v>15.24</v>
+        <v>15.37</v>
       </c>
       <c r="M148" s="9" t="n">
         <v>0.12</v>
@@ -10978,7 +10970,7 @@
       </c>
       <c r="Q148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -10994,7 +10986,7 @@
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>3.515</v>
+        <v>3.54</v>
       </c>
       <c r="D149" s="6" t="n">
         <v>5.85</v>
@@ -11003,13 +10995,13 @@
         <v>3.47</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>0.0391</v>
+        <v>0.0371</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="H149" s="7" t="n">
-        <v>0.1565</v>
+        <v>0.1483</v>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
@@ -11017,13 +11009,13 @@
         </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>117.17</v>
+        <v>118</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0.48</v>
@@ -11045,7 +11037,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11053,7 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>4.76</v>
+        <v>4.85</v>
       </c>
       <c r="D150" s="6" t="n">
         <v>8.205</v>
@@ -11070,13 +11062,13 @@
         <v>3.34</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.0304</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0609</v>
       </c>
       <c r="H150" s="7" t="n">
-        <v>0.143</v>
+        <v>0.1218</v>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
@@ -11084,13 +11076,13 @@
         </is>
       </c>
       <c r="J150" s="5" t="n">
-        <v>14.14</v>
+        <v>14.39</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M150" s="5" t="n">
         <v>0.54</v>
@@ -11112,7 +11104,7 @@
       </c>
       <c r="Q150" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11120,7 @@
         </is>
       </c>
       <c r="C151" s="6" t="n">
-        <v>2.635</v>
+        <v>2.66</v>
       </c>
       <c r="D151" s="6" t="n">
         <v>2.69</v>
@@ -11137,13 +11129,13 @@
         <v>2.22</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>-0.0054</v>
+        <v>-0.0077</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>-0.0107</v>
+        <v>-0.0153</v>
       </c>
       <c r="H151" s="7" t="n">
-        <v>-0.0214</v>
+        <v>-0.0306</v>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
@@ -11151,13 +11143,13 @@
         </is>
       </c>
       <c r="J151" s="5" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>8.81</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M151" s="5" t="n">
         <v>0.41</v>
@@ -11179,7 +11171,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11187,7 @@
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="D152" s="10" t="n">
         <v>2.69</v>
@@ -11204,13 +11196,13 @@
         <v>1.695</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>0.0133</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G152" s="11" t="n">
-        <v>0.0266</v>
+        <v>-0.0013</v>
       </c>
       <c r="H152" s="11" t="n">
-        <v>0.0531</v>
+        <v>-0.0025</v>
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
@@ -11218,13 +11210,13 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>11.24</v>
+        <v>11.66</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="L152" s="9" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="M152" s="9" t="n">
         <v>4.1</v>
@@ -11246,7 +11238,7 @@
       </c>
       <c r="Q152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:49</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11254,7 @@
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>37.5</v>
+        <v>38.02</v>
       </c>
       <c r="D153" s="6" t="n">
         <v>43.32</v>
@@ -11271,13 +11263,13 @@
         <v>32.69</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>-0.0274</v>
+        <v>-0.0305</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>-0.0548</v>
+        <v>-0.0609</v>
       </c>
       <c r="H153" s="7" t="n">
-        <v>-0.1097</v>
+        <v>-0.1219</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
@@ -11285,13 +11277,13 @@
         </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>18.47</v>
+        <v>18.73</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
@@ -11315,7 +11307,7 @@
       </c>
       <c r="Q153" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11323,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>5.04</v>
@@ -11340,13 +11332,13 @@
         <v>2.17</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>0.1035</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>0.207</v>
+        <v>0.1748</v>
       </c>
       <c r="H154" s="11" t="n">
-        <v>0.414</v>
+        <v>0.3495</v>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
@@ -11354,13 +11346,13 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>31.4</v>
+        <v>32.9</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="L154" s="9" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="M154" s="9" t="n">
         <v>0.44</v>
@@ -11382,7 +11374,7 @@
       </c>
       <c r="Q154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11390,7 @@
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>88.29000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="D155" s="6" t="n">
         <v>95.175</v>
@@ -11407,13 +11399,13 @@
         <v>70.8</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>-0.0316</v>
+        <v>-0.0338</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>-0.0631</v>
+        <v>-0.0677</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>-0.1263</v>
+        <v>-0.1354</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
@@ -11421,13 +11413,13 @@
         </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>32.7</v>
+        <v>33.04</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>12.76</v>
+        <v>12.89</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="M155" s="5" t="n">
         <v>1.62</v>
@@ -11449,7 +11441,7 @@
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11457,7 @@
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>7.405</v>
+        <v>7.13</v>
       </c>
       <c r="D156" s="6" t="n">
         <v>9.9</v>
@@ -11474,13 +11466,13 @@
         <v>5.94</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>0.0445</v>
+        <v>0.0499</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0998</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>0.1778</v>
+        <v>0.1997</v>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
@@ -11488,13 +11480,13 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>9.369999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K156" s="5" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="M156" s="5" t="n">
         <v>0.34</v>
@@ -11516,7 +11508,7 @@
       </c>
       <c r="Q156" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11528,11 +11520,11 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>WORLEY FPO [WOR]</t>
+          <t>Worley Limited</t>
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>10.5</v>
+        <v>10.65</v>
       </c>
       <c r="D157" s="6" t="n">
         <v>14.85</v>
@@ -11541,13 +11533,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>0.0461</v>
+        <v>0.0419</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0838</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>0.1844</v>
+        <v>0.1677</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
@@ -11555,12 +11547,10 @@
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>15.91</v>
-      </c>
-      <c r="K157" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>16.14</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>1.01</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
@@ -11587,7 +11577,7 @@
       </c>
       <c r="Q157" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11599,11 +11589,11 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>WOOLWORTHS FPO [WOW]</t>
+          <t>Woolworths Group Limited</t>
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>39.56</v>
+        <v>39.79</v>
       </c>
       <c r="D158" s="6" t="n">
         <v>40.75</v>
@@ -11612,13 +11602,13 @@
         <v>25.51</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>-0.0194</v>
+        <v>-0.0208</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>-0.0389</v>
+        <v>-0.0415</v>
       </c>
       <c r="H158" s="7" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
@@ -11626,10 +11616,10 @@
         </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>80.73</v>
+        <v>81.2</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>10.43</v>
+        <v>10.49</v>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
@@ -11656,7 +11646,7 @@
       </c>
       <c r="Q158" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11662,7 @@
         </is>
       </c>
       <c r="C159" s="6" t="n">
-        <v>31.365</v>
+        <v>32.29</v>
       </c>
       <c r="D159" s="6" t="n">
         <v>35.82</v>
@@ -11681,13 +11671,13 @@
         <v>21.96</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>0.0135</v>
+        <v>0.0063</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>0.0269</v>
+        <v>0.0125</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>0.0538</v>
+        <v>0.0251</v>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
@@ -11695,13 +11685,13 @@
         </is>
       </c>
       <c r="J159" s="5" t="n">
-        <v>15.37</v>
+        <v>15.91</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>4.59</v>
+        <v>4.73</v>
       </c>
       <c r="M159" s="5" t="n">
         <v>0.34</v>
@@ -11723,7 +11713,7 @@
       </c>
       <c r="Q159" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11729,7 @@
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="D160" s="6" t="n">
         <v>2.82</v>
@@ -11748,13 +11738,13 @@
         <v>2.29</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>0.019</v>
+        <v>0.0179</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0357</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
@@ -11762,13 +11752,13 @@
         </is>
       </c>
       <c r="J160" s="5" t="n">
-        <v>8.27</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>155</v>
+        <v>155.62</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="M160" s="5" t="n">
         <v>0.49</v>
@@ -11790,7 +11780,7 @@
       </c>
       <c r="Q160" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11806,22 +11796,22 @@
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>33.36</v>
+        <v>34.71</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>120.84</v>
+        <v>120.65</v>
       </c>
       <c r="E161" s="10" t="n">
         <v>28.76</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>0.2701</v>
+        <v>0.2479</v>
       </c>
       <c r="G161" s="11" t="n">
-        <v>0.5403</v>
+        <v>0.4958</v>
       </c>
       <c r="H161" s="11" t="n">
-        <v>1.0806</v>
+        <v>0.9916</v>
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
@@ -11829,13 +11819,13 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>48.35</v>
+        <v>50.3</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>4.26</v>
+        <v>4.44</v>
       </c>
       <c r="L161" s="9" t="n">
-        <v>10.48</v>
+        <v>10.91</v>
       </c>
       <c r="M161" s="9" t="n">
         <v>1.33</v>
@@ -11857,7 +11847,7 @@
       </c>
       <c r="Q161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11873,7 +11863,7 @@
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>66.315</v>
+        <v>67.69</v>
       </c>
       <c r="D162" s="10" t="n">
         <v>181.88</v>
@@ -11882,13 +11872,13 @@
         <v>61.45</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>0.2358</v>
+        <v>0.2149</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>0.4715</v>
+        <v>0.4298</v>
       </c>
       <c r="H162" s="11" t="n">
-        <v>0.9431</v>
+        <v>0.8597</v>
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
@@ -11896,13 +11886,13 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>33.13</v>
+        <v>34.48</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="L162" s="9" t="n">
-        <v>4.18</v>
+        <v>4.26</v>
       </c>
       <c r="M162" s="9" t="n">
         <v>0.39</v>
@@ -11924,7 +11914,7 @@
       </c>
       <c r="Q162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11930,7 @@
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="D163" s="10" t="n">
         <v>4.93</v>
@@ -11949,13 +11939,13 @@
         <v>1.375</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>0.1313</v>
+        <v>0.1462</v>
       </c>
       <c r="G163" s="11" t="n">
-        <v>0.2626</v>
+        <v>0.2924</v>
       </c>
       <c r="H163" s="11" t="n">
-        <v>0.5253</v>
+        <v>0.5849</v>
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
@@ -11963,13 +11953,13 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>33.25</v>
+        <v>32</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>5.09</v>
+        <v>4.89</v>
       </c>
       <c r="L163" s="9" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="M163" s="9" t="n">
         <v>3.82</v>
@@ -11991,7 +11981,7 @@
       </c>
       <c r="Q163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12120,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>0.39</v>
@@ -12139,13 +12129,13 @@
         <v>0.094</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0.04</v>
+        <v>0.0521</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>0.08</v>
+        <v>0.1042</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>0.16</v>
+        <v>0.2083</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
@@ -12153,13 +12143,13 @@
         </is>
       </c>
       <c r="J2" s="9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="L2" s="9" t="n">
-        <v>-334.24</v>
+        <v>-320.87</v>
       </c>
       <c r="M2" s="9" t="n">
         <v>1.39</v>
@@ -12181,7 +12171,7 @@
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12246,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12262,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1.217</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2.65</v>
@@ -12281,13 +12271,13 @@
         <v>0.76</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.1543</v>
+        <v>0.16</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.3201</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.6172</v>
+        <v>0.6402</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
@@ -12295,13 +12285,13 @@
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7.23</v>
+        <v>7.13</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>9.56</v>
+        <v>9.43</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>1.28</v>
@@ -12323,7 +12313,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12329,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0.16</v>
@@ -12367,10 +12357,10 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>54.72</v>
+        <v>53.38</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.62</v>
@@ -12392,7 +12382,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12398,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0.27</v>
@@ -12417,13 +12407,13 @@
         <v>0.113</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.2153</v>
+        <v>2.12</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.4306</v>
+        <v>4.24</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8.8613</v>
+        <v>8.4801</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -12431,13 +12421,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-10.49</v>
+        <v>-10.92</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5.98</v>
+        <v>6.24</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>154.04</v>
+        <v>160.46</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>2.66</v>
@@ -12459,7 +12449,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12475,22 +12465,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0.46</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.6415</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.2229</v>
+        <v>1.283</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2.4457</v>
+        <v>2.5659</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -12498,13 +12488,13 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-1.13</v>
+        <v>-1.09</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>11.24</v>
+        <v>10.86</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.12</v>
@@ -12526,7 +12516,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12542,7 +12532,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>6.6</v>
@@ -12551,13 +12541,13 @@
         <v>3.2</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.137</v>
+        <v>0.1374</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.274</v>
+        <v>0.2747</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -12565,13 +12555,13 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>13.27</v>
+        <v>13.19</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.1</v>
@@ -12593,7 +12583,7 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12609,7 +12599,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>0.892</v>
@@ -12618,13 +12608,13 @@
         <v>0.255</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.2995</v>
+        <v>0.3056</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.5989</v>
+        <v>0.6111</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>1.1978</v>
+        <v>1.2222</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -12637,10 +12627,10 @@
         </is>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.66</v>
@@ -12662,7 +12652,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12678,22 +12668,22 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>14.4</v>
+        <v>14.47</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>21.72</v>
+        <v>21.21</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>8.26</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.1576</v>
+        <v>0.1556</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.3152</v>
+        <v>0.3113</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.6304</v>
+        <v>0.6226</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -12701,13 +12691,13 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>181.68</v>
+        <v>207.43</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>6.07</v>
+        <v>6.1</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>1.12</v>
@@ -12729,7 +12719,7 @@
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12754,13 +12744,13 @@
         <v>0.155</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.142</v>
+        <v>0.1426</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.2841</v>
+        <v>0.2852</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.5682</v>
+        <v>0.5704</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -12796,7 +12786,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12802,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>9.48</v>
+        <v>9.15</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>15.1</v>
@@ -12821,13 +12811,13 @@
         <v>6.03</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.0694</v>
+        <v>0.0799</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.1388</v>
+        <v>0.1597</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.2776</v>
+        <v>0.3195</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -12835,13 +12825,13 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>39.22</v>
+        <v>40.69</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>17.14</v>
+        <v>16.55</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.19</v>
@@ -12863,7 +12853,7 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12869,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>18.605</v>
+        <v>18.43</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>21.75</v>
@@ -12888,13 +12878,13 @@
         <v>10.11</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.0195</v>
+        <v>0.0213</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.0391</v>
+        <v>0.0425</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -12902,13 +12892,13 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>43.27</v>
+        <v>42.86</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>6.74</v>
+        <v>6.68</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>7.59</v>
@@ -12930,7 +12920,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12936,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.837</v>
+        <v>0.855</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>1.295</v>
@@ -12955,13 +12945,13 @@
         <v>0.665</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.115</v>
+        <v>0.1073</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.2301</v>
+        <v>0.2147</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.4601</v>
+        <v>0.4294</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -12969,13 +12959,13 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>16.74</v>
+        <v>17.1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.11</v>
@@ -12997,7 +12987,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13056,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13072,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0.155</v>
@@ -13091,13 +13081,13 @@
         <v>0.033</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.9292</v>
+        <v>0.9074</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1.8585</v>
+        <v>1.8148</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3.717</v>
+        <v>3.6296</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -13105,10 +13095,10 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.15</v>
@@ -13133,7 +13123,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13149,7 +13139,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>2.75</v>
@@ -13158,13 +13148,13 @@
         <v>1.05</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.2736</v>
+        <v>0.2784</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.5473</v>
+        <v>0.5568</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>1.0946</v>
+        <v>1.1136</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -13172,13 +13162,13 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-30.49</v>
+        <v>-30.21</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>-1093.64</v>
+        <v>-1083.78</v>
       </c>
       <c r="M17" s="9" t="n">
         <v>1.45</v>
@@ -13200,7 +13190,7 @@
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13265,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13291,7 +13281,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>0.695</v>
@@ -13300,13 +13290,13 @@
         <v>0.19</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.2647</v>
+        <v>0.2548</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.5294</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>1.0588</v>
+        <v>1.0192</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -13314,13 +13304,13 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>-21.96</v>
+        <v>-15.65</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>58.25</v>
+        <v>59.39</v>
       </c>
       <c r="M19" s="9" t="n">
         <v>0.77</v>
@@ -13342,7 +13332,7 @@
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13348,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1.36</v>
+        <v>1.315</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>2.97</v>
@@ -13367,13 +13357,13 @@
         <v>1.23</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.136</v>
+        <v>0.145</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.2721</v>
+        <v>0.29</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.5441</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -13386,10 +13376,10 @@
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-580.25</v>
+        <v>-561.05</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.51</v>
@@ -13411,7 +13401,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13427,22 +13417,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.27</v>
+        <v>1.225</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="E21" s="6" t="n">
         <v>0.995</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.068</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.136</v>
+        <v>0.1593</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.2719</v>
+        <v>0.3186</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -13450,13 +13440,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>6.45</v>
+        <v>6.23</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>4.81</v>
+        <v>4.64</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.09</v>
@@ -13478,7 +13468,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13484,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>0.24</v>
+        <v>0.235</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>1.075</v>
@@ -13503,13 +13493,13 @@
         <v>0.23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.5899</v>
+        <v>0.6078</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>1.1799</v>
+        <v>1.2156</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>2.3598</v>
+        <v>2.4313</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -13517,10 +13507,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>7.27</v>
+        <v>7.12</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
@@ -13547,7 +13537,7 @@
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13553,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0.135</v>
@@ -13591,10 +13581,10 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>361.18</v>
+        <v>352.58</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0.11</v>
@@ -13616,7 +13606,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13681,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13707,22 +13697,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>7.52</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2.57</v>
+        <v>2.535</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.4927</v>
+        <v>0.5101</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.9854000000000001</v>
+        <v>1.0202</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1.9707</v>
+        <v>2.0404</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -13730,13 +13720,13 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-13.44</v>
+        <v>-13.13</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>170.62</v>
+        <v>166.72</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>4.76</v>
@@ -13758,7 +13748,7 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13823,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13849,13 +13839,13 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0.28</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="F27" s="7" t="n">
         <v/>
@@ -13875,10 +13865,10 @@
         <v>0.26</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-2.42</v>
+        <v>-2.34</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -13902,7 +13892,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13967,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14042,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -14068,13 +14058,13 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>1.015</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="F30" s="7" t="n">
         <v/>
@@ -14091,13 +14081,13 @@
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-1.52</v>
+        <v>-1.47</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>24.71</v>
+        <v>23.83</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0.62</v>
@@ -14119,7 +14109,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14125,7 @@
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>18.61</v>
+        <v>17.85</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>22.22</v>
@@ -14144,13 +14134,13 @@
         <v>6.4</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.0587</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.1175</v>
+        <v>0.1438</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.235</v>
+        <v>0.2875</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -14158,13 +14148,13 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>92.23999999999999</v>
+        <v>88.47</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>6.62</v>
+        <v>6.35</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>17.68</v>
+        <v>16.96</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>0.18</v>
@@ -14186,7 +14176,7 @@
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:47</t>
         </is>
       </c>
     </row>
@@ -14202,7 +14192,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>8.890000000000001</v>
@@ -14211,13 +14201,13 @@
         <v>1.95</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.2158</v>
+        <v>0.2516</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0.4315</v>
+        <v>0.5032</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>0.8631</v>
+        <v>1.0064</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -14225,13 +14215,13 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-51.96</v>
+        <v>-48.25</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>15.51</v>
+        <v>14.4</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>129.07</v>
+        <v>119.85</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>0.48</v>
@@ -14253,7 +14243,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14318,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14334,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>3.065</v>
+        <v>3.08</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>5.16</v>
@@ -14353,13 +14343,13 @@
         <v>2.43</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.1688</v>
+        <v>0.1667</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.3376</v>
+        <v>0.3335</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.6752</v>
+        <v>0.667</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -14367,13 +14357,13 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>12.26</v>
+        <v>12.32</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>1.49</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>2.21</v>
@@ -14395,7 +14385,7 @@
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14460,7 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14476,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.265</v>
+        <v>0.26</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0.325</v>
@@ -14495,13 +14485,13 @@
         <v>0.075</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.1368</v>
+        <v>0.1442</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.2736</v>
+        <v>0.2885</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.5472</v>
+        <v>0.5769</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -14509,10 +14499,10 @@
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-13.25</v>
+        <v>-13</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -14539,7 +14529,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14551,11 +14541,11 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ARAFURA FPO [ARU]</t>
+          <t>Arafura Rare Earths Limited</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.19</v>
+        <v>0.185</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>0.62</v>
@@ -14564,13 +14554,13 @@
         <v>0.17</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1351</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2703</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.5</v>
+        <v>0.5405</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -14578,10 +14568,10 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-84.06999999999999</v>
+        <v>-81.86</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
@@ -14608,7 +14598,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14624,7 +14614,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0.058</v>
@@ -14633,13 +14623,13 @@
         <v>0.015</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2.4167</v>
+        <v>2.25</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>4.8333</v>
+        <v>4.5</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>9.666700000000001</v>
+        <v>9</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -14647,13 +14637,13 @@
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-3.75</v>
+        <v>-4</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>63.64</v>
+        <v>67.89</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0.09</v>
@@ -14675,7 +14665,7 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14750,7 +14740,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14756,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.202</v>
+        <v>0.195</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>0.38</v>
@@ -14775,13 +14765,13 @@
         <v>0.095</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.245</v>
+        <v>0.2628</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0.4901</v>
+        <v>0.5256</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.9802</v>
+        <v>1.0513</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
@@ -14794,7 +14784,7 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
@@ -14821,7 +14811,7 @@
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14827,7 @@
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="D41" s="6" t="n">
         <v>0.29</v>
@@ -14865,10 +14855,10 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-9075.639999999999</v>
+        <v>-9277.32</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -14892,7 +14882,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14955,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14971,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0.135</v>
+        <v>0.12</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>0.31</v>
@@ -15009,7 +14999,7 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
@@ -15036,7 +15026,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -15111,7 +15101,7 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15117,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>0.26</v>
@@ -15155,10 +15145,10 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>1116.98</v>
+        <v>1098.96</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.46</v>
@@ -15180,7 +15170,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28 00:50</t>
+          <t>2026-07-28 23:48</t>
         </is>
       </c>
     </row>
